--- a/LISTAS_ORDENADAS/MA/Bisagras/BISAGRAS EXTRA REFORZADA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Bisagras/BISAGRAS EXTRA REFORZADA DISMAY.xlsx
@@ -826,14 +826,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45208.62714108441</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -875,26 +871,10 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="1.5" customHeight="1" s="1"/>
     <row r="28" ht="1.5" customHeight="1" s="1"/>
     <row r="29" ht="1.5" customHeight="1" s="1"/>
     <row r="30" ht="1.5" customHeight="1" s="1"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="27" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
       </c>
       <c r="C33" s="34" t="n"/>
       <c r="D33" s="35" t="n">
-        <v>652.8099999999999</v>
+        <v>652.812</v>
       </c>
       <c r="E33" s="36" t="n"/>
       <c r="F33" s="36" t="n"/>
@@ -945,7 +925,7 @@
       </c>
       <c r="C34" s="32" t="n"/>
       <c r="D34" s="38" t="n">
-        <v>1123.7</v>
+        <v>1123.703</v>
       </c>
       <c r="E34" s="36" t="n"/>
       <c r="F34" s="36" t="n"/>
@@ -964,7 +944,7 @@
       </c>
       <c r="C35" s="32" t="n"/>
       <c r="D35" s="38" t="n">
-        <v>1242.1</v>
+        <v>1242.108</v>
       </c>
       <c r="E35" s="36" t="n"/>
       <c r="F35" s="36" t="n"/>
@@ -987,7 +967,6 @@
       <c r="C37" s="40" t="n"/>
       <c r="D37" s="40" t="n"/>
     </row>
-    <row r="38"/>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
@@ -997,15 +976,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
